--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_208_R21.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_208_R21.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.4728</v>
+        <v>4.9886</v>
       </c>
       <c r="E2" t="n">
-        <v>5.9142</v>
+        <v>4.7661</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5586</v>
+        <v>0.2225</v>
       </c>
       <c r="G2" t="n">
         <v>2.2094</v>
@@ -610,13 +610,13 @@
         <v>0.4639</v>
       </c>
       <c r="S2" t="n">
-        <v>3.1217</v>
+        <v>1.6375</v>
       </c>
       <c r="T2" t="n">
-        <v>2.4812</v>
+        <v>1.333</v>
       </c>
       <c r="U2" t="n">
-        <v>0.6405</v>
+        <v>0.3044</v>
       </c>
       <c r="V2" t="n">
         <v>0.6778999999999999</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.1838</v>
+        <v>4.2846</v>
       </c>
       <c r="E3" t="n">
         <v>2.6033</v>
       </c>
       <c r="F3" t="n">
-        <v>1.5805</v>
+        <v>1.6813</v>
       </c>
       <c r="G3" t="n">
         <v>3.0473</v>
@@ -688,13 +688,13 @@
         <v>2.0876</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.9510999999999999</v>
+        <v>-0.8502999999999999</v>
       </c>
       <c r="T3" t="n">
         <v>-0.2908</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.6603</v>
+        <v>-0.5594</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. PARRA</t>
+          <t>K. PUNTER</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.0588</v>
+        <v>3.8928</v>
       </c>
       <c r="E4" t="n">
-        <v>1.7294</v>
+        <v>1.7038</v>
       </c>
       <c r="F4" t="n">
-        <v>1.3294</v>
+        <v>2.189</v>
       </c>
       <c r="G4" t="n">
-        <v>0.8614000000000001</v>
+        <v>1.1705</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5067</v>
+        <v>-0.0241</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3547</v>
+        <v>1.1946</v>
       </c>
       <c r="J4" t="n">
-        <v>0.6044</v>
+        <v>0.7276</v>
       </c>
       <c r="K4" t="n">
-        <v>0.4572</v>
+        <v>0.2625</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1472</v>
+        <v>0.465</v>
       </c>
       <c r="M4" t="n">
-        <v>0.257</v>
+        <v>0.4429</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0495</v>
+        <v>-0.2866</v>
       </c>
       <c r="O4" t="n">
-        <v>0.2075</v>
+        <v>0.7296</v>
       </c>
       <c r="P4" t="n">
-        <v>1.8556</v>
+        <v>0.4639</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-2.3195</v>
       </c>
       <c r="R4" t="n">
-        <v>1.8556</v>
+        <v>2.7834</v>
       </c>
       <c r="S4" t="n">
-        <v>1.2722</v>
+        <v>0.114</v>
       </c>
       <c r="T4" t="n">
-        <v>0.9831</v>
+        <v>-0.0626</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2891</v>
+        <v>0.1766</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.9304</v>
+        <v>2.1444</v>
       </c>
       <c r="W4" t="n">
-        <v>0.1418</v>
+        <v>3.3584</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.0722</v>
+        <v>-1.214</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>T. SATORANSKY</t>
+          <t>T. SHENGELIA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.2068</v>
+        <v>2.7345</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8338</v>
+        <v>2.4572</v>
       </c>
       <c r="F5" t="n">
-        <v>1.373</v>
+        <v>0.2773</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.6292</v>
+        <v>3.9552</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.0035</v>
+        <v>1.4189</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.6257</v>
+        <v>2.5363</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0823</v>
+        <v>4.4774</v>
       </c>
       <c r="K5" t="n">
-        <v>0.4404</v>
+        <v>1.5698</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.3581</v>
+        <v>2.9076</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.7115</v>
+        <v>-0.5222</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.4439</v>
+        <v>-0.1509</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.2676</v>
+        <v>-0.3713</v>
       </c>
       <c r="P5" t="n">
-        <v>2.0876</v>
+        <v>-0.232</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-2.3195</v>
       </c>
       <c r="R5" t="n">
         <v>2.0876</v>
       </c>
       <c r="S5" t="n">
-        <v>0.6067</v>
+        <v>0.0835</v>
       </c>
       <c r="T5" t="n">
-        <v>0.6097</v>
+        <v>0.1575</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0031</v>
+        <v>-0.074</v>
       </c>
       <c r="V5" t="n">
-        <v>0.1418</v>
+        <v>-1.0722</v>
       </c>
       <c r="W5" t="n">
         <v>0.1418</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-1.214</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>K. PUNTER</t>
+          <t>J. PARRA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.171</v>
+        <v>2.2406</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6541</v>
+        <v>0.9784</v>
       </c>
       <c r="F6" t="n">
-        <v>1.5168</v>
+        <v>1.2622</v>
       </c>
       <c r="G6" t="n">
-        <v>1.1705</v>
+        <v>0.8614000000000001</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.0241</v>
+        <v>0.5067</v>
       </c>
       <c r="I6" t="n">
-        <v>1.1946</v>
+        <v>0.3547</v>
       </c>
       <c r="J6" t="n">
-        <v>0.7276</v>
+        <v>0.6044</v>
       </c>
       <c r="K6" t="n">
-        <v>0.2625</v>
+        <v>0.4572</v>
       </c>
       <c r="L6" t="n">
-        <v>0.465</v>
+        <v>0.1472</v>
       </c>
       <c r="M6" t="n">
-        <v>0.4429</v>
+        <v>0.257</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.2866</v>
+        <v>0.0495</v>
       </c>
       <c r="O6" t="n">
-        <v>0.7296</v>
+        <v>0.2075</v>
       </c>
       <c r="P6" t="n">
-        <v>0.4639</v>
+        <v>1.8556</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.3195</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.7834</v>
+        <v>1.8556</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.6078</v>
+        <v>0.454</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.1123</v>
+        <v>0.2322</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.4955</v>
+        <v>0.2219</v>
       </c>
       <c r="V6" t="n">
-        <v>2.1444</v>
+        <v>-0.9304</v>
       </c>
       <c r="W6" t="n">
-        <v>3.3584</v>
+        <v>0.1418</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.214</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>T. SHENGELIA</t>
+          <t>T. SATORANSKY</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.8274</v>
+        <v>2.2046</v>
       </c>
       <c r="E7" t="n">
-        <v>1.7181</v>
+        <v>0.8652</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1093</v>
+        <v>1.3394</v>
       </c>
       <c r="G7" t="n">
-        <v>3.9552</v>
+        <v>-0.6292</v>
       </c>
       <c r="H7" t="n">
-        <v>1.4189</v>
+        <v>-0.0035</v>
       </c>
       <c r="I7" t="n">
-        <v>2.5363</v>
+        <v>-0.6257</v>
       </c>
       <c r="J7" t="n">
-        <v>4.4774</v>
+        <v>0.0823</v>
       </c>
       <c r="K7" t="n">
-        <v>1.5698</v>
+        <v>0.4404</v>
       </c>
       <c r="L7" t="n">
-        <v>2.9076</v>
+        <v>-0.3581</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.5222</v>
+        <v>-0.7115</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.1509</v>
+        <v>-0.4439</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.3713</v>
+        <v>-0.2676</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.232</v>
+        <v>2.0876</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.3195</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
         <v>2.0876</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.8237</v>
+        <v>0.6045</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.5816</v>
+        <v>0.6411</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.242</v>
+        <v>-0.0367</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.0722</v>
+        <v>0.1418</v>
       </c>
       <c r="W7" t="n">
         <v>0.1418</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.214</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.0815</v>
+        <v>1.1239</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.3441</v>
+        <v>-0.7976</v>
       </c>
       <c r="F8" t="n">
-        <v>2.4256</v>
+        <v>1.9215</v>
       </c>
       <c r="G8" t="n">
         <v>0.8518</v>
@@ -1078,13 +1078,13 @@
         <v>1.3917</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0022</v>
+        <v>0.0402</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.7468</v>
+        <v>-0.2003</v>
       </c>
       <c r="U8" t="n">
-        <v>0.7446</v>
+        <v>0.2405</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,10 +1111,10 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.126</v>
+        <v>-0.0945</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.7592</v>
+        <v>-0.7277</v>
       </c>
       <c r="F9" t="n">
         <v>0.6332</v>
@@ -1156,10 +1156,10 @@
         <v>1.6237</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3066</v>
+        <v>-0.2752</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0474</v>
+        <v>0.0788</v>
       </c>
       <c r="U9" t="n">
         <v>-0.3541</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.4681</v>
+        <v>-0.2254</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.518</v>
+        <v>-0.4433</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0498</v>
+        <v>0.2179</v>
       </c>
       <c r="G10" t="n">
         <v>0.0949</v>
@@ -1234,13 +1234,13 @@
         <v>0.9278</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.4187</v>
+        <v>-0.1759</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3734</v>
+        <v>-0.2987</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0452</v>
+        <v>0.1228</v>
       </c>
       <c r="V10" t="n">
         <v>-1.0722</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>D. BRIZUELA</t>
+          <t>N. LAPROVITTOLA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,58 +1267,58 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.4865</v>
+        <v>-0.4807</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.113</v>
+        <v>-1.9699</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.3735</v>
+        <v>1.4892</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.6578000000000001</v>
+        <v>0.4069</v>
       </c>
       <c r="H11" t="n">
-        <v>0.3025</v>
+        <v>2.3276</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.9603</v>
+        <v>-1.9208</v>
       </c>
       <c r="J11" t="n">
-        <v>0.111</v>
+        <v>0.1607</v>
       </c>
       <c r="K11" t="n">
-        <v>0.8605</v>
+        <v>2.289</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.7495000000000001</v>
+        <v>-2.1283</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.7688</v>
+        <v>0.2462</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.5581</v>
+        <v>0.0387</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.2108</v>
+        <v>0.2075</v>
       </c>
       <c r="P11" t="n">
-        <v>0.6959</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-2.3195</v>
       </c>
       <c r="R11" t="n">
-        <v>0.6959</v>
+        <v>1.3917</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.5245</v>
+        <v>0.0402</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.224</v>
+        <v>0.1889</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3005</v>
+        <v>-0.1487</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>N. LAPROVITTOLA</t>
+          <t>D. BRIZUELA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,58 +1345,58 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.9264</v>
+        <v>-0.5537</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.5164</v>
+        <v>-0.113</v>
       </c>
       <c r="F12" t="n">
-        <v>1.59</v>
+        <v>-0.4407</v>
       </c>
       <c r="G12" t="n">
-        <v>0.4069</v>
+        <v>-0.6578000000000001</v>
       </c>
       <c r="H12" t="n">
-        <v>2.3276</v>
+        <v>0.3025</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.9208</v>
+        <v>-0.9603</v>
       </c>
       <c r="J12" t="n">
-        <v>0.1607</v>
+        <v>0.111</v>
       </c>
       <c r="K12" t="n">
-        <v>2.289</v>
+        <v>0.8605</v>
       </c>
       <c r="L12" t="n">
-        <v>-2.1283</v>
+        <v>-0.7495000000000001</v>
       </c>
       <c r="M12" t="n">
-        <v>0.2462</v>
+        <v>-0.7688</v>
       </c>
       <c r="N12" t="n">
-        <v>0.0387</v>
+        <v>-0.5581</v>
       </c>
       <c r="O12" t="n">
-        <v>0.2075</v>
+        <v>-0.2108</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.9278</v>
+        <v>0.6959</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.3195</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.3917</v>
+        <v>0.6959</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.4055</v>
+        <v>-0.5917</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.3576</v>
+        <v>-0.224</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0479</v>
+        <v>-0.3677</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>18.9951</v>
+        <v>20.1153</v>
       </c>
       <c r="E13" t="n">
-        <v>8.202200000000001</v>
+        <v>9.322500000000002</v>
       </c>
       <c r="F13" t="n">
-        <v>10.7927</v>
+        <v>10.7928</v>
       </c>
       <c r="G13" t="n">
         <v>9.867400000000002</v>
@@ -1438,7 +1438,7 @@
         <v>9.8672</v>
       </c>
       <c r="I13" t="n">
-        <v>-2.220446049250313e-16</v>
+        <v>-1.110223024625157e-16</v>
       </c>
       <c r="J13" t="n">
         <v>11.8183</v>
@@ -1456,7 +1456,7 @@
         <v>-2.7045</v>
       </c>
       <c r="O13" t="n">
-        <v>0.7537000000000001</v>
+        <v>0.7537</v>
       </c>
       <c r="P13" t="n">
         <v>9.2782</v>
@@ -1468,10 +1468,10 @@
         <v>17.3965</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.03949999999999948</v>
+        <v>1.0808</v>
       </c>
       <c r="T13" t="n">
-        <v>0.4349</v>
+        <v>1.5551</v>
       </c>
       <c r="U13" t="n">
         <v>-0.4744</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.4054</v>
+        <v>1.9729</v>
       </c>
       <c r="E14" t="n">
-        <v>2.2745</v>
+        <v>2.6284</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.8692</v>
+        <v>-0.6555</v>
       </c>
       <c r="G14" t="n">
         <v>-0.6844</v>
@@ -1546,13 +1546,13 @@
         <v>0.6959</v>
       </c>
       <c r="S14" t="n">
-        <v>0.4635</v>
+        <v>1.031</v>
       </c>
       <c r="T14" t="n">
-        <v>0.2636</v>
+        <v>0.6173999999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1999</v>
+        <v>0.4136</v>
       </c>
       <c r="V14" t="n">
         <v>0.9304</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6418</v>
+        <v>1.2873</v>
       </c>
       <c r="E15" t="n">
-        <v>2.1275</v>
+        <v>2.4814</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.4857</v>
+        <v>-1.1941</v>
       </c>
       <c r="G15" t="n">
         <v>-0.7833</v>
@@ -1624,13 +1624,13 @@
         <v>0.9278</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.4332</v>
+        <v>0.2124</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.1098</v>
+        <v>0.244</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.3233</v>
+        <v>-0.0316</v>
       </c>
       <c r="V15" t="n">
         <v>0.9304</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>I. BONGA</t>
+          <t>N. CALATHES</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.5641</v>
+        <v>0.2434</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.0927</v>
+        <v>0.4475</v>
       </c>
       <c r="F16" t="n">
-        <v>1.6568</v>
+        <v>-0.2041</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.3532</v>
+        <v>-0.4869</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.0048</v>
+        <v>0.9519</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.3485</v>
+        <v>-1.4388</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.6949</v>
+        <v>1.2611</v>
       </c>
       <c r="K16" t="n">
-        <v>0.9649</v>
+        <v>2.1713</v>
       </c>
       <c r="L16" t="n">
-        <v>-1.6597</v>
+        <v>-0.9102</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.6583</v>
+        <v>-1.7481</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.9696</v>
+        <v>-1.2195</v>
       </c>
       <c r="O16" t="n">
-        <v>0.3113</v>
+        <v>-0.5286</v>
       </c>
       <c r="P16" t="n">
-        <v>1.1598</v>
+        <v>-0.232</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.232</v>
+        <v>-1.1598</v>
       </c>
       <c r="R16" t="n">
-        <v>1.3917</v>
+        <v>0.9278</v>
       </c>
       <c r="S16" t="n">
-        <v>1.1518</v>
+        <v>0.9623</v>
       </c>
       <c r="T16" t="n">
-        <v>0.2284</v>
+        <v>0.3462</v>
       </c>
       <c r="U16" t="n">
-        <v>0.9234</v>
+        <v>0.6161</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.3943</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.3943</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>B. FERNANDO</t>
+          <t>I. BONGA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4195</v>
+        <v>-0.08649999999999999</v>
       </c>
       <c r="E17" t="n">
-        <v>0.951</v>
+        <v>-1.5645</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.5315</v>
+        <v>1.478</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.4639</v>
+        <v>-1.3532</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.8488</v>
+        <v>-0.0048</v>
       </c>
       <c r="I17" t="n">
-        <v>0.3849</v>
+        <v>-1.3485</v>
       </c>
       <c r="J17" t="n">
-        <v>0.6554</v>
+        <v>-0.6949</v>
       </c>
       <c r="K17" t="n">
-        <v>0.5818</v>
+        <v>0.9649</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0736</v>
+        <v>-1.6597</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.1194</v>
+        <v>-0.6583</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.4306</v>
+        <v>-0.9696</v>
       </c>
       <c r="O17" t="n">
         <v>0.3113</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.4639</v>
+        <v>1.1598</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.1598</v>
+        <v>-0.232</v>
       </c>
       <c r="R17" t="n">
-        <v>0.6959</v>
+        <v>1.3917</v>
       </c>
       <c r="S17" t="n">
-        <v>1.3473</v>
+        <v>0.5012</v>
       </c>
       <c r="T17" t="n">
-        <v>1.3135</v>
+        <v>-0.2434</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0338</v>
+        <v>0.7446</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>-0.3943</v>
       </c>
       <c r="W17" t="n">
-        <v>0.1418</v>
+        <v>-0.3943</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.1418</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>N. CALATHES</t>
+          <t>B. FERNANDO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.9583</v>
+        <v>-0.9052</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.4961</v>
+        <v>-0.2285</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4622</v>
+        <v>-0.6767</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.4869</v>
+        <v>-0.4639</v>
       </c>
       <c r="H18" t="n">
-        <v>0.9519</v>
+        <v>-0.8488</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.4388</v>
+        <v>0.3849</v>
       </c>
       <c r="J18" t="n">
-        <v>1.2611</v>
+        <v>0.6554</v>
       </c>
       <c r="K18" t="n">
-        <v>2.1713</v>
+        <v>0.5818</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.9102</v>
+        <v>0.0736</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.7481</v>
+        <v>-1.1194</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.2195</v>
+        <v>-1.4306</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.5286</v>
+        <v>0.3113</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.232</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q18" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R18" t="n">
-        <v>0.9278</v>
+        <v>0.6959</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.2394</v>
+        <v>0.0226</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.5975</v>
+        <v>0.134</v>
       </c>
       <c r="U18" t="n">
-        <v>0.358</v>
+        <v>-0.1114</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>T. JEKIRI</t>
+          <t>J. PARKER</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.2525</v>
+        <v>-1.4837</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.4459</v>
+        <v>-2.0376</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1935</v>
+        <v>0.5538999999999999</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.5721</v>
+        <v>-1.4797</v>
       </c>
       <c r="H19" t="n">
-        <v>-2.88</v>
+        <v>-0.7971</v>
       </c>
       <c r="I19" t="n">
-        <v>0.3079</v>
+        <v>-0.6826</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.3602</v>
+        <v>-1.5188</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.9858</v>
+        <v>-0.7324000000000001</v>
       </c>
       <c r="L19" t="n">
-        <v>0.6257</v>
+        <v>-0.7863</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.212</v>
+        <v>0.0391</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.8942</v>
+        <v>-0.06469999999999999</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.3178</v>
+        <v>0.1038</v>
       </c>
       <c r="P19" t="n">
-        <v>-2.7834</v>
+        <v>0.232</v>
       </c>
       <c r="Q19" t="n">
-        <v>-3.7112</v>
+        <v>-0.232</v>
       </c>
       <c r="R19" t="n">
-        <v>0.9278</v>
+        <v>0.4639</v>
       </c>
       <c r="S19" t="n">
-        <v>4.1031</v>
+        <v>-0.2359</v>
       </c>
       <c r="T19" t="n">
-        <v>3.4836</v>
+        <v>-0.2869</v>
       </c>
       <c r="U19" t="n">
-        <v>0.6194</v>
+        <v>0.051</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.1418</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. PARKER</t>
+          <t>D. WASHINGTON</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,64 +1969,64 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.5851</v>
+        <v>-1.688</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.2735</v>
+        <v>0.1111</v>
       </c>
       <c r="F20" t="n">
-        <v>0.6884</v>
+        <v>-1.7991</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.4797</v>
+        <v>1.7265</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.7971</v>
+        <v>0.2543</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.6826</v>
+        <v>1.4722</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.5188</v>
+        <v>3.7181</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.7324000000000001</v>
+        <v>2.3464</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.7863</v>
+        <v>1.3717</v>
       </c>
       <c r="M20" t="n">
-        <v>0.0391</v>
+        <v>-1.9916</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.06469999999999999</v>
+        <v>-2.0921</v>
       </c>
       <c r="O20" t="n">
-        <v>0.1038</v>
+        <v>0.1005</v>
       </c>
       <c r="P20" t="n">
-        <v>0.232</v>
+        <v>-5.3349</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.232</v>
+        <v>-5.7988</v>
       </c>
       <c r="R20" t="n">
         <v>0.4639</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.3374</v>
+        <v>-0.224</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.5228</v>
+        <v>0.0474</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1854</v>
+        <v>-0.2715</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>2.1444</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>2.1444</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>D. WASHINGTON</t>
+          <t>T. JEKIRI</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.215</v>
+        <v>-3.4035</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.8325</v>
+        <v>-3.687</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.3825</v>
+        <v>0.2835</v>
       </c>
       <c r="G21" t="n">
-        <v>1.7265</v>
+        <v>-2.5721</v>
       </c>
       <c r="H21" t="n">
-        <v>0.2543</v>
+        <v>-2.88</v>
       </c>
       <c r="I21" t="n">
-        <v>1.4722</v>
+        <v>0.3079</v>
       </c>
       <c r="J21" t="n">
-        <v>3.7181</v>
+        <v>-1.3602</v>
       </c>
       <c r="K21" t="n">
-        <v>2.3464</v>
+        <v>-1.9858</v>
       </c>
       <c r="L21" t="n">
-        <v>1.3717</v>
+        <v>0.6257</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.9916</v>
+        <v>-1.212</v>
       </c>
       <c r="N21" t="n">
-        <v>-2.0921</v>
+        <v>-0.8942</v>
       </c>
       <c r="O21" t="n">
-        <v>0.1005</v>
+        <v>-0.3178</v>
       </c>
       <c r="P21" t="n">
-        <v>-5.3349</v>
+        <v>-2.7834</v>
       </c>
       <c r="Q21" t="n">
-        <v>-5.7988</v>
+        <v>-3.7112</v>
       </c>
       <c r="R21" t="n">
-        <v>0.4639</v>
+        <v>0.9278</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.751</v>
+        <v>1.952</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.8962</v>
+        <v>1.2426</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.8549</v>
+        <v>0.7095</v>
       </c>
       <c r="V21" t="n">
-        <v>2.1444</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>2.1444</v>
+        <v>0.1418</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.6453</v>
+        <v>-3.6281</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.1776</v>
+        <v>-2.0597</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.4677</v>
+        <v>-1.5685</v>
       </c>
       <c r="G22" t="n">
         <v>-1.0983</v>
@@ -2170,13 +2170,13 @@
         <v>0.232</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.5469000000000001</v>
+        <v>-0.5298</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2987</v>
+        <v>-0.1808</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2482</v>
+        <v>-0.349</v>
       </c>
       <c r="V22" t="n">
         <v>-1.0722</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.4374</v>
+        <v>-4.5395</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.8485</v>
+        <v>-3.3767</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.5889</v>
+        <v>-1.1628</v>
       </c>
       <c r="G23" t="n">
         <v>-1.4775</v>
@@ -2248,13 +2248,13 @@
         <v>0.9278</v>
       </c>
       <c r="S23" t="n">
-        <v>-2.1403</v>
+        <v>-1.2423</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.2696</v>
+        <v>-0.7978</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.8707</v>
+        <v>-0.4446</v>
       </c>
       <c r="V23" t="n">
         <v>-1.3558</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.9322</v>
+        <v>-5.1915</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.9791</v>
+        <v>-3.5073</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.9531</v>
+        <v>-1.6842</v>
       </c>
       <c r="G24" t="n">
         <v>-1.1944</v>
@@ -2326,13 +2326,13 @@
         <v>0.4639</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.578</v>
+        <v>-0.8373</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.1202</v>
+        <v>-0.6484</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.4577</v>
+        <v>-0.1889</v>
       </c>
       <c r="V24" t="n">
         <v>-1.0722</v>
@@ -2359,22 +2359,22 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-18.995</v>
+        <v>-17.4224</v>
       </c>
       <c r="E25" t="n">
         <v>-10.7929</v>
       </c>
       <c r="F25" t="n">
-        <v>-8.202099999999998</v>
+        <v>-6.6296</v>
       </c>
       <c r="G25" t="n">
-        <v>-9.867199999999999</v>
+        <v>-9.8672</v>
       </c>
       <c r="H25" t="n">
         <v>-9.8674</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>1.110223024625157e-16</v>
       </c>
       <c r="J25" t="n">
         <v>1.9509</v>
@@ -2404,13 +2404,13 @@
         <v>8.118400000000001</v>
       </c>
       <c r="S25" t="n">
-        <v>0.03950000000000053</v>
+        <v>1.612200000000001</v>
       </c>
       <c r="T25" t="n">
-        <v>0.4742999999999995</v>
+        <v>0.4743000000000001</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.4348999999999998</v>
+        <v>1.1378</v>
       </c>
       <c r="V25" t="n">
         <v>0.1107</v>
